--- a/dataset/Faulty/memory_allocation_failure.xlsx
+++ b/dataset/Faulty/memory_allocation_failure.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -456,14 +456,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -478,14 +478,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,14 +500,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -522,14 +522,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -561,19 +561,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>#define MAX_VAL UINT_MAX #define MAX 10 #define MAX_10 429496730 #define ERROR 0x1 #define MAX_V 4294967295UL unsigned int memory_allocation_failure_005_gbl = 65536; char * memory_allocation_failure_007_str_gbl; memory_allocation_failure_010_s_001 *memory_allocation_failure_010_arr_gbl; void *vptr; int **memory_allocation_failure_006_gbl_doubleptr; static unsigned int static_var = MAX_VAL*2; enum {max_buffer = MAX_VAL*2}; memory_allocation_failure_011_uni_001 * memory_allocation_failure_011_gbl_u1; int *memory_allocation_failure_012_buf2_gbl; static int staticflag=1; const int arr_value[2] = {1,MAX_VAL}; int * memory_allocation_failure_015_gbl_ptr; int * memory_allocation_failure_016_gbl_ptr1; int * memory_allocation_failure_016_gbl_ptr2; extern volatile int vflag; void memory_allocation_failure_006() { int flag=0,i; if(memory_allocation_failure_006_func_001(flag)==0) { memory_allocation_failure_006_func_002(); } if(memory_allocation_failure_006_func_001(flag)==0) { for(i=0;i&lt;10;i++) { if(memory_allocation_failure_006_gbl_doubleptr[i]!=NULL) { free (memory_allocation_failure_006_gbl_doubleptr[i]); memory_allocation_failure_006_gbl_doubleptr[i] = NULL; } } free(memory_allocation_failure_006_gbl_doubleptr); memory_allocation_failure_006_gbl_doubleptr = NULL; } } void memory_allocation_failure_006_func_002() { int i; if(memory_allocation_failure_006_func_001(0)==0) { memory_allocation_failure_006_gbl_doubleptr=(int**) malloc(10*sizeof(int*)); for(i=0;i&lt;10;i++) { memory_allocation_failure_006_gbl_doubleptr[i]=(int*) malloc(MAX_10*sizeof(int));/*Tool should detect this line as error*/ /*ERROR:Memory allocation failure */ memory_allocation_failure_006_gbl_doubleptr[i][0] =10; } } } int memory_allocation_failure_006_func_001(int flag) { int ret; if (flag ==0) ret = 0; else ret=1; return ret; }</t>
+          <t>#define MAX_VAL UINT_MAX #define MAX 10 #define MAX_10 429496730 #define ERROR 0x1 #define MAX_V 4294967295UL unsigned int memory_allocation_failure_005_gbl = 65536; char * memory_allocation_failure_007_str_gbl; memory_allocation_failure_010_s_001 *memory_allocation_failure_010_arr_gbl; void *vptr; int **memory_allocation_failure_006_gbl_doubleptr; static unsigned int static_var = MAX_VAL*2; enum {max_buffer = MAX_VAL*2}; memory_allocation_failure_011_uni_001 * memory_allocation_failure_011_gbl_u1; int *memory_allocation_failure_012_buf2_gbl; static int staticflag=1; const int arr_value[2] = {1,MAX_VAL}; int * memory_allocation_failure_015_gbl_ptr; int * memory_allocation_failure_016_gbl_ptr1; int * memory_allocation_failure_016_gbl_ptr2; extern volatile int vflag; void memory_allocation_failure_006() { int flag=0,i; if(memory_allocation_failure_006_func_001(flag)==0) { memory_allocation_failure_006_func_002(); } if(memory_allocation_failure_006_func_001(flag)==0) { for(i=0;i&lt;10;i++) { if(memory_allocation_failure_006_gbl_doubleptr[i]!=NULL) { free (memory_allocation_failure_006_gbl_doubleptr[i]); memory_allocation_failure_006_gbl_doubleptr[i] = NULL; } } free(memory_allocation_failure_006_gbl_doubleptr); memory_allocation_failure_006_gbl_doubleptr = NULL; } } int memory_allocation_failure_006_func_001(int flag) { int ret; if (flag ==0) ret = 0; else ret=1; return ret; } void memory_allocation_failure_006_func_002() { int i; if(memory_allocation_failure_006_func_001(0)==0) { memory_allocation_failure_006_gbl_doubleptr=(int**) malloc(10*sizeof(int*)); for(i=0;i&lt;10;i++) { memory_allocation_failure_006_gbl_doubleptr[i]=(int*) malloc(MAX_10*sizeof(int));/*Tool should detect this line as error*/ /*ERROR:Memory allocation failure */ memory_allocation_failure_006_gbl_doubleptr[i][0] =10; } } }</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -588,14 +588,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -610,14 +610,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -632,14 +632,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -654,14 +654,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>#define MAX_VAL UINT_MAX #define MAX 10 #define ERROR 0x1 #define MAX_V 4294967295UL typedef struct { int *a; int b; } memory_allocation_failure_011_s_001; typedef union { memory_allocation_failure_011_s_001 *s1; memory_allocation_failure_011_s_002 *s2; memory_allocation_failure_011_s_003 *s3; } memory_allocation_failure_011_uni_001; unsigned int memory_allocation_failure_005_gbl = 65536; char * memory_allocation_failure_007_str_gbl; memory_allocation_failure_010_s_001 *memory_allocation_failure_010_arr_gbl; void *vptr; int **memory_allocation_failure_006_gbl_doubleptr; static unsigned int static_var = MAX_VAL*2; enum {max_buffer = MAX_VAL*2}; memory_allocation_failure_011_uni_001 * memory_allocation_failure_011_gbl_u1; int *memory_allocation_failure_012_buf2_gbl; static int staticflag=1; const int arr_value[2] = {1,MAX_VAL}; int * memory_allocation_failure_015_gbl_ptr; int * memory_allocation_failure_016_gbl_ptr1; int * memory_allocation_failure_016_gbl_ptr2; extern volatile int vflag; void memory_allocation_failure_011 () { memory_allocation_failure_011_uni_001 *p =NULL; memory_allocation_failure_011_func_002(); if( memory_allocation_failure_011_gbl_u1 != NULL) { p = memory_allocation_failure_011_gbl_u1; p-&gt;s1-&gt;a[1] = 10; free(memory_allocation_failure_011_gbl_u1-&gt;s1-&gt;a); free(memory_allocation_failure_011_gbl_u1-&gt;s1); free(memory_allocation_failure_011_gbl_u1); } } void memory_allocation_failure_011_func_002(void) { memory_allocation_failure_011_gbl_u1 = (memory_allocation_failure_011_uni_001 * )malloc(memory_allocation_failure_011_func_001(0)*sizeof( memory_allocation_failure_011_uni_001 )); /*Tool should detect this line as error*/ /*ERROR:Memory allocation failure */ memory_allocation_failure_011_gbl_u1-&gt;s1 = (memory_allocation_failure_011_s_001 *) malloc(sizeof(memory_allocation_failure_011_s_001)); memory_allocation_failure_011_gbl_u1-&gt;s1-&gt;a = (int *) calloc ( 5,sizeof(int)); } int memory_allocation_failure_011_func_001(int flag) { int ret =0; if (flag ==0) ret = MAX_VAL; else ret=5; return ret; }</t>
+          <t>#define MAX_VAL UINT_MAX #define MAX 10 #define ERROR 0x1 #define MAX_V 4294967295UL typedef union { memory_allocation_failure_011_s_001 *s1; memory_allocation_failure_011_s_002 *s2; memory_allocation_failure_011_s_003 *s3; } memory_allocation_failure_011_uni_001; typedef struct { int *a; int b; } memory_allocation_failure_011_s_001; unsigned int memory_allocation_failure_005_gbl = 65536; char * memory_allocation_failure_007_str_gbl; memory_allocation_failure_010_s_001 *memory_allocation_failure_010_arr_gbl; void *vptr; int **memory_allocation_failure_006_gbl_doubleptr; static unsigned int static_var = MAX_VAL*2; enum {max_buffer = MAX_VAL*2}; memory_allocation_failure_011_uni_001 * memory_allocation_failure_011_gbl_u1; int *memory_allocation_failure_012_buf2_gbl; static int staticflag=1; const int arr_value[2] = {1,MAX_VAL}; int * memory_allocation_failure_015_gbl_ptr; int * memory_allocation_failure_016_gbl_ptr1; int * memory_allocation_failure_016_gbl_ptr2; extern volatile int vflag; void memory_allocation_failure_011 () { memory_allocation_failure_011_uni_001 *p =NULL; memory_allocation_failure_011_func_002(); if( memory_allocation_failure_011_gbl_u1 != NULL) { p = memory_allocation_failure_011_gbl_u1; p-&gt;s1-&gt;a[1] = 10; free(memory_allocation_failure_011_gbl_u1-&gt;s1-&gt;a); free(memory_allocation_failure_011_gbl_u1-&gt;s1); free(memory_allocation_failure_011_gbl_u1); } } void memory_allocation_failure_011_func_002(void) { memory_allocation_failure_011_gbl_u1 = (memory_allocation_failure_011_uni_001 * )malloc(memory_allocation_failure_011_func_001(0)*sizeof( memory_allocation_failure_011_uni_001 )); /*Tool should detect this line as error*/ /*ERROR:Memory allocation failure */ memory_allocation_failure_011_gbl_u1-&gt;s1 = (memory_allocation_failure_011_s_001 *) malloc(sizeof(memory_allocation_failure_011_s_001)); memory_allocation_failure_011_gbl_u1-&gt;s1-&gt;a = (int *) calloc ( 5,sizeof(int)); } int memory_allocation_failure_011_func_001(int flag) { int ret =0; if (flag ==0) ret = MAX_VAL; else ret=5; return ret; }</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,14 +698,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -720,14 +720,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -764,14 +764,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/memory_allocation_failure.c</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
